--- a/etf_holdings/2026-08-25_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-25_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,135 +464,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00403A(15,000)</t>
+          <t>00982A(2,000)、00403A(100,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>00980A(-11,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>智邦科技</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>00991A(-50,000)、00982A(-90,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>00981A(113,000)、00403A(60,000)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00981A(12,000)、00985A(17,000)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>00980A(22,000)、00403A(120,000)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
